--- a/S_数据表/EquipSuit_Template.xlsx
+++ b/S_数据表/EquipSuit_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\YongShi\S_数据表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C53DF6-8581-43C5-BE3D-51393E19B0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A28314-4485-488E-A6DF-35FB0BD0FD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="254">
   <si>
     <t>ID</t>
   </si>
@@ -783,6 +783,34 @@
   </si>
   <si>
     <t>10030307;10030308;10030309</t>
+  </si>
+  <si>
+    <t>不朽套装1</t>
+  </si>
+  <si>
+    <t>不朽套装2</t>
+  </si>
+  <si>
+    <t>不朽套装3</t>
+  </si>
+  <si>
+    <t>不朽套装4</t>
+  </si>
+  <si>
+    <t>2,15811</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,15821;3,15822;4,15823</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,15831</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,15841</t>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3943,7 +3971,7 @@
         <v>1581</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>171</v>
@@ -3955,7 +3983,7 @@
         <v>16</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="G63" s="4"/>
     </row>
@@ -3964,7 +3992,7 @@
         <v>1582</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>171</v>
@@ -3976,7 +4004,7 @@
         <v>185</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="G64" s="4"/>
     </row>
@@ -3985,7 +4013,7 @@
         <v>1583</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>171</v>
@@ -3997,7 +4025,7 @@
         <v>16</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="G65" s="4"/>
     </row>
@@ -4006,7 +4034,7 @@
         <v>1584</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>171</v>
@@ -4018,7 +4046,7 @@
         <v>21</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="G66" s="4"/>
     </row>
